--- a/IMRADS/TALISAY/Datasets/Talisay shelter data.xlsx
+++ b/IMRADS/TALISAY/Datasets/Talisay shelter data.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PERSONAL\BRYAN\bulsu\Thesis 1\ShelterAlloc_Thesis\IMRADS\TALISAY\Datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD308796-BF1F-4B8F-B875-37DF0B732DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE4E2C6-D6CE-4C09-B2D6-5B77C64D8CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$L$11</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
   <si>
     <t>Remarks</t>
   </si>
@@ -69,44 +72,50 @@
     <t>Longitude</t>
   </si>
   <si>
-    <t>Darasa Brgy. Hall</t>
-  </si>
-  <si>
-    <t>San Antonio Brgy. Hall</t>
-  </si>
-  <si>
-    <t>Tagaytay Unida Church</t>
-  </si>
-  <si>
-    <t>Maugat Gymnasium</t>
-  </si>
-  <si>
-    <t>Suplang Covered Court</t>
-  </si>
-  <si>
-    <t>City EC of Sto. Tomas</t>
-  </si>
-  <si>
-    <t>Brgy. Asis-3 EC</t>
-  </si>
-  <si>
     <t>BUILT</t>
   </si>
   <si>
-    <t>Santa Clara Brgy. Hall</t>
+    <t>PEDRO ALEGRE AURE SENIORHIGH SCHOOL</t>
   </si>
   <si>
-    <t>Brgy. San Jose BB Court</t>
+    <t>SILANG JUNCTION SOUTH</t>
   </si>
   <si>
-    <t>San Fernando Brgy. Hall</t>
+    <t>SUPLANG</t>
+  </si>
+  <si>
+    <t>LUYOS</t>
+  </si>
+  <si>
+    <t>DAYAPAN ELEMENTARY SCHOOL</t>
+  </si>
+  <si>
+    <t>SAMBAT</t>
+  </si>
+  <si>
+    <t>TRAPICHE BASKETBALL COURT</t>
+  </si>
+  <si>
+    <t>TINURIK</t>
+  </si>
+  <si>
+    <t>POBLACION</t>
+  </si>
+  <si>
+    <t>SANTA CLARA</t>
+  </si>
+  <si>
+    <t>EMPTY LOT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000000000000"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -141,16 +150,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -158,11 +178,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -171,6 +206,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -392,13 +436,14 @@
   <dimension ref="A1:W999"/>
   <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.109375" customWidth="1"/>
+    <col min="1" max="1" width="34.33203125" customWidth="1"/>
     <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="16" customWidth="1"/>
     <col min="8" max="10" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -447,30 +492,27 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2">
-        <v>14.03111</v>
-      </c>
-      <c r="C2">
-        <v>121.20647</v>
-      </c>
-      <c r="D2">
-        <v>152.37</v>
+    <row r="2" spans="1:23" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="6">
+        <v>14.128169362551599</v>
+      </c>
+      <c r="C2" s="6">
+        <v>120.907726226305</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1287</v>
       </c>
       <c r="E2">
-        <f>7700 * D2</f>
-        <v>1173249</v>
+        <v>9909900</v>
       </c>
       <c r="F2">
-        <f>2*D2</f>
-        <v>304.74</v>
+        <v>2574</v>
       </c>
       <c r="G2">
-        <f>60000*D2</f>
-        <v>9142200</v>
+        <v>77220000</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -481,34 +523,31 @@
       <c r="J2" t="b">
         <v>1</v>
       </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3">
-        <v>13.75380344</v>
-      </c>
-      <c r="C3">
-        <v>121.0448988</v>
-      </c>
-      <c r="D3">
-        <v>52.35</v>
+      <c r="K2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6">
+        <v>14.112577200951799</v>
+      </c>
+      <c r="C3" s="6">
+        <v>120.950728605929</v>
+      </c>
+      <c r="D3" s="5">
+        <v>41839</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E11" si="0">7700 * D3</f>
-        <v>403095</v>
+        <v>3033327500</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F10" si="1">2*D3</f>
-        <v>104.7</v>
+        <v>83678</v>
       </c>
       <c r="G3">
-        <f>60000*D3</f>
-        <v>3141000</v>
+        <v>5543667500</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -519,34 +558,31 @@
       <c r="J3" t="b">
         <v>1</v>
       </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4">
-        <v>14.06742611</v>
-      </c>
-      <c r="C4">
-        <v>121.1531806</v>
-      </c>
-      <c r="D4">
-        <v>247.08</v>
+      <c r="K3" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="6">
+        <v>14.1480401302936</v>
+      </c>
+      <c r="C4" s="6">
+        <v>121.062539475015</v>
+      </c>
+      <c r="D4" s="5">
+        <v>500</v>
       </c>
       <c r="E4">
-        <f t="shared" si="0"/>
-        <v>1902516</v>
+        <v>3850000</v>
       </c>
       <c r="F4">
-        <f t="shared" si="1"/>
-        <v>494.16</v>
+        <v>1000</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G11" si="2">60000*D4</f>
-        <v>14824800</v>
+        <v>30000000</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -557,34 +593,31 @@
       <c r="J4" t="b">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5">
-        <v>13.85590172</v>
-      </c>
-      <c r="C5">
-        <v>120.9720927</v>
-      </c>
-      <c r="D5">
-        <v>98.79</v>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="6">
+        <v>14.125290063879399</v>
+      </c>
+      <c r="C5" s="6">
+        <v>121.069190907867</v>
+      </c>
+      <c r="D5" s="5">
+        <v>7532</v>
       </c>
       <c r="E5">
-        <f t="shared" si="0"/>
-        <v>760683</v>
+        <v>546070000</v>
       </c>
       <c r="F5">
-        <f t="shared" si="1"/>
-        <v>197.58</v>
+        <v>15064</v>
       </c>
       <c r="G5">
-        <f t="shared" si="2"/>
-        <v>5927400</v>
+        <v>997990000</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -595,34 +628,31 @@
       <c r="J5" t="b">
         <v>1</v>
       </c>
-      <c r="K5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6">
-        <v>14.086450230000001</v>
-      </c>
-      <c r="C6">
-        <v>120.9815912</v>
-      </c>
-      <c r="D6">
-        <v>152.24</v>
+      <c r="K5" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="6">
+        <v>14.1034107746757</v>
+      </c>
+      <c r="C6" s="6">
+        <v>121.07866781522701</v>
+      </c>
+      <c r="D6" s="5">
+        <v>213</v>
       </c>
       <c r="E6">
-        <f t="shared" si="0"/>
-        <v>1172248</v>
+        <v>1640100</v>
       </c>
       <c r="F6">
-        <f t="shared" si="1"/>
-        <v>304.48</v>
+        <v>426</v>
       </c>
       <c r="G6">
-        <f>60000*D6</f>
-        <v>9134400</v>
+        <v>12780000</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -633,34 +663,31 @@
       <c r="J6" t="b">
         <v>1</v>
       </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7">
-        <v>14.08572015</v>
-      </c>
-      <c r="C7">
-        <v>120.6811275</v>
-      </c>
-      <c r="D7">
-        <v>774.17</v>
+      <c r="K6" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="6">
+        <v>14.087718970289099</v>
+      </c>
+      <c r="C7" s="6">
+        <v>121.131365660596</v>
+      </c>
+      <c r="D7" s="5">
+        <v>11669</v>
       </c>
       <c r="E7">
-        <f t="shared" si="0"/>
-        <v>5961109</v>
+        <v>846002500</v>
       </c>
       <c r="F7">
-        <f t="shared" si="1"/>
-        <v>1548.34</v>
+        <v>23338</v>
       </c>
       <c r="G7">
-        <f t="shared" si="2"/>
-        <v>46450200</v>
+        <v>1546142500</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -671,34 +698,31 @@
       <c r="J7" t="b">
         <v>1</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8">
-        <v>13.736448729999999</v>
-      </c>
-      <c r="C8">
-        <v>121.17764940000001</v>
-      </c>
-      <c r="D8">
-        <v>575.54</v>
+      <c r="B8" s="6">
+        <v>14.093628056827701</v>
+      </c>
+      <c r="C8" s="6">
+        <v>121.13006639414699</v>
+      </c>
+      <c r="D8" s="5">
+        <v>571</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
-        <v>4431658</v>
+        <v>4396700</v>
       </c>
       <c r="F8">
-        <f t="shared" si="1"/>
-        <v>1151.08</v>
+        <v>1142</v>
       </c>
       <c r="G8">
-        <f t="shared" si="2"/>
-        <v>34532400</v>
+        <v>34260000</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -709,34 +733,31 @@
       <c r="J8" t="b">
         <v>1</v>
       </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>14.151772100000001</v>
-      </c>
-      <c r="C9">
-        <v>121.0650424</v>
-      </c>
-      <c r="D9">
-        <v>144.55000000000001</v>
+      <c r="K8" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6">
+        <v>14.065199715509801</v>
+      </c>
+      <c r="C9" s="6">
+        <v>121.124897300963</v>
+      </c>
+      <c r="D9" s="5">
+        <v>283</v>
       </c>
       <c r="E9">
-        <f t="shared" si="0"/>
-        <v>1113035</v>
+        <v>20517500</v>
       </c>
       <c r="F9">
-        <f t="shared" si="1"/>
-        <v>289.10000000000002</v>
+        <v>566</v>
       </c>
       <c r="G9">
-        <f>60000*D9</f>
-        <v>8673000</v>
+        <v>37497500</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -747,34 +768,31 @@
       <c r="J9" t="b">
         <v>1</v>
       </c>
-      <c r="K9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>14.106979389999999</v>
-      </c>
-      <c r="C10">
-        <v>121.1390664</v>
-      </c>
-      <c r="D10">
-        <v>616.63</v>
+      <c r="K9" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="6">
+        <v>14.042537009765001</v>
+      </c>
+      <c r="C10" s="6">
+        <v>121.155138720845</v>
+      </c>
+      <c r="D10" s="5">
+        <v>688</v>
       </c>
       <c r="E10">
-        <f t="shared" si="0"/>
-        <v>4748051</v>
+        <v>49880000</v>
       </c>
       <c r="F10">
-        <f t="shared" si="1"/>
-        <v>1233.26</v>
+        <v>1376</v>
       </c>
       <c r="G10">
-        <f>60000*D10</f>
-        <v>36997800</v>
+        <v>91160000</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -785,34 +803,31 @@
       <c r="J10" t="b">
         <v>1</v>
       </c>
-      <c r="K10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11">
-        <v>14.138158600000001</v>
-      </c>
-      <c r="C11">
-        <v>120.9013801</v>
-      </c>
-      <c r="D11">
-        <v>63.38</v>
+      <c r="K10" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="6">
+        <v>14.0227401463126</v>
+      </c>
+      <c r="C11" s="6">
+        <v>121.199052277807</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1726</v>
       </c>
       <c r="E11">
-        <f t="shared" si="0"/>
-        <v>488026</v>
+        <v>125135000</v>
       </c>
       <c r="F11">
-        <f>2*D11</f>
-        <v>126.76</v>
+        <v>3452</v>
       </c>
       <c r="G11">
-        <f t="shared" si="2"/>
-        <v>3802800</v>
+        <v>228695000</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -823,11 +838,14 @@
       <c r="J11" t="b">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="13.2" x14ac:dyDescent="0.25"/>
+      <c r="K11" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
     <row r="13" spans="1:23" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="K13" s="3"/>
@@ -4753,8 +4771,8 @@
       <c r="E999" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L11" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>